--- a/ksoft/docs/records/Payment_Term_Records.xlsx
+++ b/ksoft/docs/records/Payment_Term_Records.xlsx
@@ -12201,13 +12201,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8654BEAE-C9F2-4D8F-ADE8-06F641905DA0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DA6D253-D8C6-407D-91DD-326056571B42}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39B58AEF-F4E0-4719-9D6F-7A83361E1B2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9569AE1-2E73-48D9-A55E-FE6A1B79D0C7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE55168-9E07-4270-82ED-30A7DBA4122B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31F946F4-0ACA-4796-996F-89293BDDBBDD}"/>
 </file>
--- a/ksoft/docs/records/Payment_Term_Records.xlsx
+++ b/ksoft/docs/records/Payment_Term_Records.xlsx
@@ -12201,13 +12201,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DA6D253-D8C6-407D-91DD-326056571B42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8654BEAE-C9F2-4D8F-ADE8-06F641905DA0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9569AE1-2E73-48D9-A55E-FE6A1B79D0C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39B58AEF-F4E0-4719-9D6F-7A83361E1B2A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31F946F4-0ACA-4796-996F-89293BDDBBDD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE55168-9E07-4270-82ED-30A7DBA4122B}"/>
 </file>